--- a/Lab_python/lab4_new/lab4.5_new/lab4.5_new/рост_по_товарам.xlsx
+++ b/Lab_python/lab4_new/lab4.5_new/lab4.5_new/рост_по_товарам.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-6.3</v>
+        <v>-10.3</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-11.9</v>
+        <v>-0.9</v>
       </c>
       <c r="C3" t="n">
-        <v>9.5</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-3</v>
+        <v>-4.6</v>
       </c>
       <c r="C4" t="n">
-        <v>-10.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-24.1</v>
+        <v>32.3</v>
       </c>
       <c r="C5" t="n">
-        <v>-18.2</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Lab_python/lab4_new/lab4.5_new/lab4.5_new/рост_по_товарам.xlsx
+++ b/Lab_python/lab4_new/lab4.5_new/lab4.5_new/рост_по_товарам.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-10.3</v>
+        <v>42.3</v>
       </c>
       <c r="C2" t="n">
-        <v>-7</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9</v>
+        <v>48.5</v>
       </c>
       <c r="C3" t="n">
-        <v>16.7</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.6</v>
+        <v>-50</v>
       </c>
       <c r="C4" t="n">
-        <v>4.9</v>
+        <v>-62.2</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.3</v>
+        <v>-21.8</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
